--- a/DateBase/orders/Nha Thu_2026-6-8.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-8.xlsx
@@ -524,7 +524,7 @@
         <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F11" t="str">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -584,7 +584,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030311681081520515</v>
+        <v>030311681081520513</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-8.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-8.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -527,9 +527,92 @@
         <v>13</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>188_戴安娜_Diana_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>5</v>
+      </c>
+      <c r="C21" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -584,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030311681081520513</v>
+        <v>03031168108152051315721025105100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-8.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-8.xlsx
@@ -606,9 +606,6 @@
       <c r="A21" t="str">
         <v>5</v>
       </c>
-      <c r="C21" t="str">
-        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-6-8.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-8.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -606,10 +606,76 @@
       <c r="A21" t="str">
         <v>5</v>
       </c>
+      <c r="C21" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>533_风车果_scabiosa pods_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>329_柔丝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="C26" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>6</v>
+      </c>
+      <c r="C27" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L28"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +730,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03031168108152051315721025105100</v>
+        <v>030311681081520513157210251051051010510204530</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-8.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-8.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -673,9 +673,17 @@
         <v>30</v>
       </c>
     </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L29"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -730,7 +738,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030311681081520513157210251051051010510204530</v>
+        <v>03031168108152051315721025105105101051020453010</v>
       </c>
     </row>
   </sheetData>
